--- a/diseases/d097/2026-2029.xlsx
+++ b/diseases/d097/2026-2029.xlsx
@@ -8171,6 +8171,151 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>333</v>
+      </c>
+      <c r="O49" t="n">
+        <v>333</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.09540576982122052</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8204,7 +8349,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8432,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -8297,7 +8442,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -8349,7 +8494,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12097</v>
+        <v>12430</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d097/2026-2029.xlsx
+++ b/diseases/d097/2026-2029.xlsx
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O27" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O28" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="O34" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -6119,10 +6119,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="O35" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6933,81 +6933,92 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>358</v>
+        <v>169</v>
       </c>
       <c r="O40" t="n">
-        <v>358</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.102568365153144</v>
+        <v>169</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7034,17 +7045,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7069,7 +7080,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -7078,81 +7089,170 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>874</v>
+        <v>169</v>
       </c>
       <c r="O41" t="n">
-        <v>874</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.2504043328040443</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>169</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary cyclosporiasis notifications.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7314,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -7223,13 +7323,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2275</v>
+        <v>358</v>
       </c>
       <c r="O42" t="n">
-        <v>2275</v>
+        <v>358</v>
       </c>
       <c r="R42" t="n">
-        <v>0.6517961752050351</v>
+        <v>0.102568365153144</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -7359,7 +7459,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -7368,13 +7468,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2163</v>
+        <v>874</v>
       </c>
       <c r="O43" t="n">
-        <v>2163</v>
+        <v>874</v>
       </c>
       <c r="R43" t="n">
-        <v>0.619707748118018</v>
+        <v>0.2504043328040443</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -7504,22 +7604,22 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2393</v>
+        <v>2275</v>
       </c>
       <c r="O44" t="n">
-        <v>2393</v>
+        <v>2275</v>
       </c>
       <c r="R44" t="n">
-        <v>0.6856036251717139</v>
+        <v>0.6517961752050351</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7649,22 +7749,22 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1538</v>
+        <v>2163</v>
       </c>
       <c r="O45" t="n">
-        <v>1538</v>
+        <v>2163</v>
       </c>
       <c r="R45" t="n">
-        <v>0.4406428648199315</v>
+        <v>0.619707748118018</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -7794,7 +7894,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -7803,13 +7903,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>931</v>
+        <v>2393</v>
       </c>
       <c r="O46" t="n">
-        <v>931</v>
+        <v>2393</v>
       </c>
       <c r="R46" t="n">
-        <v>0.2667350501608298</v>
+        <v>0.6856036251717139</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7939,7 +8039,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7948,13 +8048,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>530</v>
+        <v>1538</v>
       </c>
       <c r="O47" t="n">
-        <v>530</v>
+        <v>1538</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1518470210367774</v>
+        <v>0.4406428648199315</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -8084,7 +8184,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -8093,13 +8193,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>327</v>
+        <v>931</v>
       </c>
       <c r="O48" t="n">
-        <v>327</v>
+        <v>931</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0936867469415589</v>
+        <v>0.2667350501608298</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8229,22 +8329,22 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>333</v>
+        <v>530</v>
       </c>
       <c r="O49" t="n">
-        <v>333</v>
+        <v>530</v>
       </c>
       <c r="R49" t="n">
-        <v>0.09540576982122052</v>
+        <v>0.1518470210367774</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8311,6 +8411,296 @@
         </is>
       </c>
       <c r="BC49" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>327</v>
+      </c>
+      <c r="O50" t="n">
+        <v>327</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.0936867469415589</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>333</v>
+      </c>
+      <c r="O51" t="n">
+        <v>333</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.09540576982122052</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -8432,7 +8822,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -8442,7 +8832,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -8462,7 +8852,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -8494,7 +8884,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12430</v>
+        <v>12610</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d097/2026-2029.xlsx
+++ b/diseases/d097/2026-2029.xlsx
@@ -8706,6 +8706,151 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>57</v>
+      </c>
+      <c r="O52" t="n">
+        <v>57</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.0163307173567855</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8739,7 +8884,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8967,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -8832,7 +8977,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -8884,7 +9029,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12610</v>
+        <v>12667</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d097/2026-2029.xlsx
+++ b/diseases/d097/2026-2029.xlsx
@@ -8851,6 +8851,151 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>38</v>
+      </c>
+      <c r="O53" t="n">
+        <v>38</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8884,7 +9029,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -8967,7 +9112,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -8977,7 +9122,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -9029,7 +9174,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12667</v>
+        <v>12705</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d097/2026-2029.xlsx
+++ b/diseases/d097/2026-2029.xlsx
@@ -8996,6 +8996,151 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>109</v>
+      </c>
+      <c r="O54" t="n">
+        <v>109</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.0312289156471863</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9029,7 +9174,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9257,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -9122,7 +9267,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -9174,7 +9319,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12705</v>
+        <v>12814</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d097/2026-2029.xlsx
+++ b/diseases/d097/2026-2029.xlsx
@@ -1166,6 +1166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1314,6 +1319,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1462,6 +1472,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1610,6 +1625,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1758,6 +1778,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2296,6 +2321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2444,6 +2474,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2592,6 +2627,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2740,6 +2780,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3278,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3426,6 +3476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3574,6 +3629,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3722,6 +3782,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3854,10 +3919,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -4010,10 +4075,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -4260,6 +4325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4408,6 +4478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4556,6 +4631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4704,6 +4784,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5242,6 +5327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5390,6 +5480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5538,6 +5633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5686,6 +5786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5831,6 +5936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5963,10 +6073,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O34" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -6119,10 +6229,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O35" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -6366,6 +6476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6511,6 +6626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6656,6 +6776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6801,6 +6926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6933,10 +7063,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="O40" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -7089,10 +7219,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="O41" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -7336,6 +7466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7481,6 +7616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7626,6 +7766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7771,6 +7916,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7864,12 +8014,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7903,81 +8053,92 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2393</v>
+        <v>22</v>
       </c>
       <c r="O46" t="n">
-        <v>2393</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0.6856036251717139</v>
+        <v>22</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8004,17 +8165,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8039,7 +8200,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -8048,81 +8209,170 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1538</v>
+        <v>22</v>
       </c>
       <c r="O47" t="n">
-        <v>1538</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.4406428648199315</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary cyclosporiasis notifications.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CYCLOSPORIASIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8434,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -8193,17 +8443,22 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>931</v>
+        <v>2393</v>
       </c>
       <c r="O48" t="n">
-        <v>931</v>
+        <v>2393</v>
       </c>
       <c r="R48" t="n">
-        <v>0.2667350501608298</v>
+        <v>0.6856036251717139</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8329,7 +8584,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -8338,17 +8593,22 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>530</v>
+        <v>1538</v>
       </c>
       <c r="O49" t="n">
-        <v>530</v>
+        <v>1538</v>
       </c>
       <c r="R49" t="n">
-        <v>0.1518470210367774</v>
+        <v>0.4406428648199315</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8474,7 +8734,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -8483,17 +8743,22 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>327</v>
+        <v>931</v>
       </c>
       <c r="O50" t="n">
-        <v>327</v>
+        <v>931</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0936867469415589</v>
+        <v>0.2667350501608298</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8619,26 +8884,31 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>333</v>
+        <v>530</v>
       </c>
       <c r="O51" t="n">
-        <v>333</v>
+        <v>530</v>
       </c>
       <c r="R51" t="n">
-        <v>0.09540576982122052</v>
+        <v>0.1518470210367774</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8764,26 +9034,31 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>57</v>
+        <v>327</v>
       </c>
       <c r="O52" t="n">
-        <v>57</v>
+        <v>327</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0163307173567855</v>
+        <v>0.0936867469415589</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8909,7 +9184,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -8918,17 +9193,22 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>38</v>
+        <v>333</v>
       </c>
       <c r="O53" t="n">
-        <v>38</v>
+        <v>333</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01088714490452366</v>
+        <v>0.09540576982122052</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -9054,7 +9334,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -9063,17 +9343,22 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="O54" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0312289156471863</v>
+        <v>0.0163307173567855</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9136,6 +9421,456 @@
         </is>
       </c>
       <c r="BC54" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>38</v>
+      </c>
+      <c r="O55" t="n">
+        <v>38</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>109</v>
+      </c>
+      <c r="O56" t="n">
+        <v>109</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.0312289156471863</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>289</v>
+      </c>
+      <c r="O57" t="n">
+        <v>289</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.08279960203703524</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -9174,7 +9909,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9992,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -9267,7 +10002,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -9287,7 +10022,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -9319,7 +10054,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12814</v>
+        <v>13135</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d097/2026-2029.xlsx
+++ b/diseases/d097/2026-2029.xlsx
@@ -1155,9 +1155,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -1308,9 +1305,6 @@
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -1461,9 +1455,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -1614,9 +1605,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -1767,9 +1755,6 @@
       <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -2310,9 +2295,6 @@
       <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -2616,9 +2598,6 @@
       <c r="O13" t="n">
         <v>3</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -2769,9 +2748,6 @@
       <c r="O14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -3312,9 +3288,6 @@
       <c r="O17" t="n">
         <v>4</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -3465,9 +3438,6 @@
       <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -3618,9 +3588,6 @@
       <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -3771,9 +3738,6 @@
       <c r="O20" t="n">
         <v>5</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -4314,9 +4278,6 @@
       <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -4467,9 +4428,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -4620,9 +4578,6 @@
       <c r="O25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -4773,9 +4728,6 @@
       <c r="O26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -5316,9 +5268,6 @@
       <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -5469,9 +5418,6 @@
       <c r="O30" t="n">
         <v>6</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -5622,9 +5568,6 @@
       <c r="O31" t="n">
         <v>6</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -5775,9 +5718,6 @@
       <c r="O32" t="n">
         <v>6</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -9871,6 +9811,156 @@
         </is>
       </c>
       <c r="BC57" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D097</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Cyclosporiasis</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>环孢子虫病</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>494</v>
+      </c>
+      <c r="O58" t="n">
+        <v>494</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.1415328837588076</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -9909,7 +9999,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -9992,7 +10082,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -10002,7 +10092,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -10054,7 +10144,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13135</v>
+        <v>13629</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d097/2026-2029.xlsx
+++ b/diseases/d097/2026-2029.xlsx
@@ -765,6 +765,11 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -777,13 +782,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -2784,6 +2799,11 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2796,13 +2816,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -4371,6 +4401,11 @@
       <c r="O27" t="n">
         <v>2</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4383,13 +4418,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -6675,6 +6720,11 @@
       <c r="O43" t="n">
         <v>5</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6687,13 +6737,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -8547,6 +8607,11 @@
       <c r="O56" t="n">
         <v>58</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8559,13 +8624,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -12726,6 +12801,11 @@
       <c r="O85" t="n">
         <v>209</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12738,13 +12818,23 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -21654,6 +21744,11 @@
       <c r="O147" t="n">
         <v>175</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21666,13 +21761,23 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
       </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV147" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -36774,6 +36879,11 @@
       <c r="O252" t="n">
         <v>22</v>
       </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36786,12 +36896,22 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
